--- a/Result/checksun_type/電力設備.xlsx
+++ b/Result/checksun_type/電力設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>118.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>123.48</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>129.32</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>129.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>6660.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>12370.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>12370.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>11313.9</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>10664.12</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>10664.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>290.3377297371826</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>6660</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>6660.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>124.02</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>129.76</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>124.02</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>129.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>29419.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>11922.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>11922.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>11723.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>10870.2</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>10870.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>944.5084424789566</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>29419</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>29419.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>116.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>124.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>130.18</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>124.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>130.18</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5943.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>9621.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>9621.200000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>9433.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>10840.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>10840.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-593.1586979784715</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5943</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5943.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>117.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>124.92</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>130.66</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>124.92</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>130.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>10780.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>12262.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>12262.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>10051.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>10994.02</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>10994.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-253.3560879898541</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>10780</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>10780.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>118.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>125.62</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>131.24</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>125.62</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>131.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>9050.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>11437.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>11437.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12216.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>11031.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>11031.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-277.1253562921902</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>9050</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>9050.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>119.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>126.25</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>131.73</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>131.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>4419.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>10257.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>10257.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11815.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>11063.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>11063.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-115.8269768565206</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>4419</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4419.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>121.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>126.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>132.23</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>132.23</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>17914.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>11525.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>11525.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>13900.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>11172.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>11172.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>614.9145286535986</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>17914</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>17914.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>127.58</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>132.75</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>127.58</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>132.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>19150.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>9246.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>9246.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>13869.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11003.34</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11003.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>190.9768747875678</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>19150</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19150.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>133.25</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>133.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>6654.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7839.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7839.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>13568.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10936.96</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>10936.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-553.8975191206046</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>6654</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>6654.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>128.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>133.68</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>128.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>133.68</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>3150.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>12996.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>12996.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>13330.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>11162.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>11162.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-259.3645990208279</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>3150</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>3150.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>125.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>128.78</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>134.13</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>128.78</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>134.13</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>10760.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>13373.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>13373.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>13784.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>11403.4</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>11403.4</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>546.0883082295968</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>10760</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>10760.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>661.0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>693.85</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>757.74</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>693.85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>757.74</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>712958.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>792037.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>792037</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>1109041.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1587746.18</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1587746.18</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-180463.9620508341</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>712958</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>712958.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>661.2</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>698.65</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>763.12</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>698.65</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>763.12</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>625808.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1047539.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1047539.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>1197029.2</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1609718.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1609718.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-173323.4371483272</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>625808</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>625808.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>654.4</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>701.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>768.9</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>701.8</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>768.9</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>643959.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>1163874.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>1163874.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>1469582.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1641057.24</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1641057.24</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-147595.0645323058</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>643959</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>643959.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>657.6</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>705.65</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>775.68</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>775.6799999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>706601.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>1264658.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>1264658.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>1638238.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1667740.04</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1667740.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-107513.7442046928</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>706601</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>706601.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>709.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>781.92</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>781.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1270859.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1337944.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1337944.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1646579.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1693766.7</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1693766.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-53126.58144364925</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1270859</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1270859.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>659.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>713.75</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>787.68</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>713.75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>787.6799999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>1990469.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>1426046.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>1426046</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1661220.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1766700.72</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1766700.72</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-33989.47101917118</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>1990469</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1990469.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>653.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>720.2</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>792.16</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>720.2</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>792.16</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1207486.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1346519.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1346519.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1548234.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1812003.46</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1812003.46</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-82537.90359066054</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1207486</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1207486.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>655.4</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>728.45</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>796.64</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>796.64</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1147878.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1775289.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1775289.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1535904.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1855325.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1855325.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-65053.98927883594</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1147878</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1147878.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>659.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>736.75</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>802.06</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>736.75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>802.0599999999999</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>1073032.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2011819.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2011819.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1515893.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1946359.3</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1946359.3</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-31367.04064484267</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>1073032</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1073032.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>679.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>747.95</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>808.66</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>747.95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>808.66</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1711365.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1955214.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1955214.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1550532.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2038998.2</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2038998.2</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>25896.6374267491</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1711365</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1711365.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>694.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>757.8</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>812.84</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>757.8</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>812.84</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1592835.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1896394.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1896394.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1630314.3</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2070739.62</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2070739.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>38384.19047806808</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1592835</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1592835.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>125.3</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>134.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>141.04</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>134.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>141.04</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>498901.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>365940.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>365940.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>479466.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1071362.34</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1071362.34</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-139227.8162722384</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>498901</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>498901.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>134.72</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>141.74</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>134.72</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>141.74</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>295387.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>362617.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>362617.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>497331.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1071880.36</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1071880.36</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-155289.580176622</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>295387</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>295387.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>125.9</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>135.5</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>142.67</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>142.67</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>267896.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>603311.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>603311.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>605514.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1078057.96</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1078057.96</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-150883.8293194333</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>267896</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>267896.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>127.6</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>143.56</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>143.56</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>411695.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>608536.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>608536.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>744226.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1081455.44</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1081455.44</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-136255.7270477555</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>411695</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>411695.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>129.9</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>137.35</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>144.37</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>137.35</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>144.37</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>355823.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>585515.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>585515</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>819050.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1078409.64</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1078409.64</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-125899.1978365104</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>355823</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>355823.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>131.4</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>137.68</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>144.98</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>144.98</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>482286.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>592992.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>592992.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1019901.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1081460.4</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1081460.4</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-100621.4704691418</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>482286</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>482286.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>133.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>137.5</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>145.37</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>145.37</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1498856.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>632046.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>632046.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1131680.8</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1075319.16</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1075319.16</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-74466.41457043169</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1498856</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1498856.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>135.4</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>137.07</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>145.78</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>137.07</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>145.78</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>294021.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>607717.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>607717.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1232806.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1049475.74</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1049475.74</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-143360.7484804732</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>294021</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>294021.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>138.9</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>136.72</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>146.2</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>136.72</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>146.2</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>296589.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>879917.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>879917.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1270495.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1053609.7</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1053609.7</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-107571.7344776583</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>296589</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>296589.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>142.3</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>146.78</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>146.78</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>393212.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1052585.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1052585.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1282174.2</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1065844.62</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1065844.62</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-52877.8668137209</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>393212</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>393212.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>143.7</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>135.82</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>147.38</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>147.38</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>677553.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1446810.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1446810.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1297394.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1114847.44</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1114847.44</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>16792.26080667996</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>677553</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>677553.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15259,11 +15061,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
           <t>2459</t>
@@ -15445,41 +15243,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr">
         <is>
           <t>0</t>
@@ -15500,20 +15294,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15320,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>0</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15489,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15673,11 @@
           <t>9.178</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>9.46</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>9.91</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>9.91</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15724,16 @@
           <t>2776890.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2668457.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2668457.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3185586.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3789125.3</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3789125.3</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15750,10 @@
           <t>-287525.4901763392</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>2776890</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>2776890.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15919,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16103,11 @@
           <t>9.138000000000002</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>9.49</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>9.93</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>9.93</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16154,16 @@
           <t>2902360.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>2582965.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>2582965.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3284249.7</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3884286.92</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3884286.92</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16180,10 @@
           <t>-290445.472212675</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2902360</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2902360.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16349,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16533,11 @@
           <t>9.144000000000002</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>9.53</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>9.96</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>9.960000000000001</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16584,16 @@
           <t>2830587.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>2847567.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>2847567.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3423020.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3906661.5</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3906661.5</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16610,10 @@
           <t>-297687.0368284159</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2830587</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2830587.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16779,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16963,11 @@
           <t>9.209999999999999</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>9.58</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>9.99</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>9.99</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17014,16 @@
           <t>2781856.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>2979518.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>2979518.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3742042.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3914932.34</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3914932.34</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17040,10 @@
           <t>-289710.4849641738</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>2781856</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>2781856.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17209,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17393,11 @@
           <t>9.322</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>9.63</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>10.02</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>10.02</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17444,16 @@
           <t>2050594.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3546572.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3546572.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>4561413.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3896092.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3896092.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17470,10 @@
           <t>-262747.4292665361</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2050594</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2050594.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17639,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17823,11 @@
           <t>9.41</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>9.67</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>10.05</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>10.05</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17874,16 @@
           <t>2349431.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>3702715.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>3702715.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>4617654.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3897912.5</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3897912.5</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17900,10 @@
           <t>-136495.4415103919</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>2349431</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>2349431.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18069,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18253,11 @@
           <t>9.524</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>9.72</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>10.08</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>10.08</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18304,16 @@
           <t>4225370.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3985533.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3985533.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>4760549.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>3919333.58</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>3919333.58</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18330,10 @@
           <t>16721.12819518521</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>4225370</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>4225370.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18499,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18683,11 @@
           <t>9.581999999999999</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>9.76</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>10.11</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10.11</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18734,16 @@
           <t>3490341.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3998474.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3998474</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>4641264.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>3893954.12</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>3893954.12</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18760,10 @@
           <t>34011.2946247533</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>3490341</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>3490341.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18929,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19113,11 @@
           <t>9.592</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>10.14</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19164,16 @@
           <t>5617125.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>4504565.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>4504565.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4712020.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>3865949.54</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>3865949.54</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19190,10 @@
           <t>136249.9504303951</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5617125</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5617125.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19359,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19543,11 @@
           <t>9.606</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>9.83</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>10.16</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>10.16</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19594,16 @@
           <t>2831311.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>5576254.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>5576254.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>4413712.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>3831619.3</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>3831619.3</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19620,10 @@
           <t>49569.38906594086</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2831311</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2831311.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19789,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19973,11 @@
           <t>9.578000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>9.86</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>10.18</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>10.18</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20024,16 @@
           <t>3763522.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>5532592.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>5532592.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>4682084.4</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3862637.42</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3862637.42</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>222449.7517929366</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3763522</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3763522.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>10702402903</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>9579043601</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>16911194399</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>15812987742</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>15882778006</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>10973548400</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>12353712685</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>10709769939</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>18182742782</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>10733728288</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>13958553198</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24949,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25133,11 @@
           <t>156.3</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>164.85</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>168.36</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>168.36</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25184,16 @@
           <t>3170553681.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>4138082091.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>4138082091</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>4268507640.2</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>6060043081.46</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>6060043081.46</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25210,10 @@
           <t>-263552895.6884155</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>3170553681</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>3170553681.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25379,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25563,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>166.68</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25614,16 @@
           <t>3561255788.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>4508528303.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>4508528303.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>4128239206.8</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>6523283246.84</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>6523283246.84</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25640,10 @@
           <t>-197408387.5697174</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>3561255788</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>3561255788.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25809,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25993,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>168.38</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26044,16 @@
           <t>5330763891.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>5326173063.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>5326173063.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>4050371893.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>6516029437.64</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>6516029437.64</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26070,10 @@
           <t>-137726873.5940866</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>5330763891</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>5330763891.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26239,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26423,11 @@
           <t>156.8</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>168.21</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>168.21</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26474,16 @@
           <t>3892624091.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>4843786138.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>4843786138.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3728171837.0</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>6576214335.28</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>6576214335.28</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26500,10 @@
           <t>-237138904.8933973</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>3892624091</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>3892624091.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26669,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26853,11 @@
           <t>158.6</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>170.58</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>167.82</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>167.82</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26904,16 @@
           <t>4735213004.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>4739633072.6</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>4739633072.6</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3540693680.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>6556873375.6</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>6556873375.6</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26930,10 @@
           <t>-216600438.7176485</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>4735213004</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>4735213004.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27099,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27283,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>170.95</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>170.95</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27334,16 @@
           <t>5022784742.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>4398933189.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>4398933189.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3348452263.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>6518094899.78</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>6518094899.78</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27360,10 @@
           <t>-269801426.3338051</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>5022784742</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>5022784742.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27529,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27713,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27764,16 @@
           <t>7649479589.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>3747950110.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>3747950110.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>3187753716.9</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>6448828659.12</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>6448828659.12</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27790,10 @@
           <t>-366978329.6306791</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>7649479589</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>7649479589.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27959,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28143,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>166.08</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>166.08</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28194,16 @@
           <t>2918829265.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2774570723.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2774570723</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>3016948267.5</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>6307955645.82</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>6307955645.82</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28220,10 @@
           <t>-774127699.0322614</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2918829265</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2918829265.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28573,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>172.2</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>165.33</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>165.33</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28624,16 @@
           <t>3371858763.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2612557535.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2612557535.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>3246709810.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>6279997636.12</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>6279997636.12</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28650,10 @@
           <t>-821266845.6405125</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3371858763</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3371858763.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28819,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29003,11 @@
           <t>166.8</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>172.52</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>164.6</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>164.6</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29054,16 @@
           <t>3031713588.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2341754288.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2341754288.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>3717183320.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>6247764195.28</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>6247764195.28</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29080,10 @@
           <t>-907816399.6651387</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3031713588</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3031713588.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29249,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29433,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>172.38</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>163.91</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>163.91</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29484,16 @@
           <t>1767869347.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>2297971337.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>2297971337.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>5310238320.6</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>6248161668.22</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>6248161668.22</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>-962592479.5337062</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1767869347</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1767869347.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
